--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>19/10 14:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>19/10 17:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>19/10 01:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>18/10 13:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>19/10 13:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>18/10 17:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>19/10 02:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>200</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>18/10 15:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>18/10 19:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>19/10 02:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>200</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>18/10 19:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>200</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>200</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>19/10 01:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>200</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>19/10 14:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>175</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>19/10 16:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>175</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>175</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>18/10 23:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>175</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>18/10 14:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>150</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/10 14:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>150</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>150</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>140</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45948.06118057081</v>
+        <v>45948.06118056713</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salzbourg – Innsbruck Die HaieAutriche - Autriche ICE - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19/10 13:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>275.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+237%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45948.12265748755</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – Fischtown PinguinsAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19/10 12:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45948.12265748755</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HC Pustert</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HC Pustertal – Black Wings LinzAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/10 16:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+140%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45948.12265748755</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Michalovce</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Michalovce – PopradSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>19/10 14:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45948.12265748755</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -1580,10 +1580,8 @@
           <t>19/10 13:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>275.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>275</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45948.12265748755</v>
+        <v>45948.12265748843</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>175</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45948.12265748755</v>
+        <v>45948.12265748843</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>19/10 16:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>175</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45948.12265748755</v>
+        <v>45948.12265748843</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>19/10 14:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>150</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45948.12265748755</v>
+        <v>45948.12265748843</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,51 @@
         <v>45948.12265748843</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Munich</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EHC Munich – Dresdner EislowenDEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19/10 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45948.22186440793</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>19/10 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,97 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45948.22186440793</v>
+        <v>45948.22186440972</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Presov – Banska BystricaExtraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19/10 14:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+121%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45948.27054550975</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Grizzlys W</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Grizzlys Wolfsburg – Adler MannheimDEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19/10 12:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45948.27054550975</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -1795,10 +1795,8 @@
           <t>19/10 14:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>150</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45948.27054550975</v>
+        <v>45948.27054550926</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45948.27054550975</v>
+        <v>45948.27054550926</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,51 @@
         <v>45948.27054550926</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Wild Wings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wild Wings – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/10 14:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45948.35175157087</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>19/10 14:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>150</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,52 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45948.35175157087</v>
+        <v>45948.35175157408</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Djurgaarde</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Djurgaardens IF – Brynas IFSHL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18/10 13:15</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+183%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45948.38917827275</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>18/10 13:15</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45948.38917827275</v>
+        <v>45948.38917827547</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EC VSV – F</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EC VSV – FTC-TelekomAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19/10 15:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+214%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45948.43083494075</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -1967,10 +1967,8 @@
           <t>19/10 15:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>225</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45948.43083494075</v>
+        <v>45948.43083494213</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,51 @@
         <v>45948.43083494213</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – SaiPaLiiga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>18/10 14:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45948.5586783273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,23 +2010,111 @@
           <t>18/10 14:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>140</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45948.55867832176</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cologne Haie – StraubingDEL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19/10 14:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>+111%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>45948.5586783273</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45948.59580799381</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Augsbourg </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Augsbourg – Lowen FrankfurtDEL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/10 14:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45948.59580799381</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>19/10 14:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>140</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45948.59580799381</v>
+        <v>45948.59580799768</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>19/10 14:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>140</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,232 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45948.59580799381</v>
+        <v>45948.59580799768</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Chicago Bl</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago Blackhawks – Anaheim DucksNHL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/10 23:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+176%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45948.63825889843</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Detroit Re</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Detroit Red Wings – Edmonton OilersNHL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/10 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45948.63825889843</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Utah Hocke</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Utah Hockey Club – Boston BruinsNHL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19/10 23:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45948.63825889843</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Washington</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Washington Capitals – Vancouver CanucksNHL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/10 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+137%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45948.63825889843</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Eisbären BerlinAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19/10 12:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+132%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45948.63825889843</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -2139,10 +2139,8 @@
           <t>19/10 23:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45948.63825889843</v>
+        <v>45948.63825890046</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>19/10 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>200</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45948.63825889843</v>
+        <v>45948.63825890046</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>19/10 23:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45948.63825889843</v>
+        <v>45948.63825890046</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>19/10 16:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>175</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45948.63825889843</v>
+        <v>45948.63825890046</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>19/10 12:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>175</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45948.63825889843</v>
+        <v>45948.63825890046</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,1131 @@
         <v>45948.63825890046</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vivasorte(BR)Football | Pas de corners1re période | Neom SC – </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vivasorte(BR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Neom SC – AL QadisiyahSaudi Arabia - Saudi Prof. League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de corners1re période</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19/10 18:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>56.10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MozzartFootball | 2 1er but | Al Nassr R</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MozzartFootball</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Al Nassr R. – Al FatehSaudi Arabia - Pro League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 1er but</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18/10 18:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bet7Football | 1 dernier but | Caracas FC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bet7Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Caracas FC – Carabobo FCVenezuela - Primera Division</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1 dernier but</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19/10 00:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetliveBasketball | Plus que 842e mi-temps + P | Kolossos –</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetliveBasketball</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kolossos – PanathinaikosGreece - A1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 842e mi-temps + P</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19/10 13:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Casa Pariurilor(RO)Football | Moins que 9.5 - tirs1re équipe | Metaloglob</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Casa Pariurilor(RO)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Metaloglobus – FCSBRomania - 1.Romania</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18/10 17:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MarathonBet(DK)Football | H 2 (−0.25) | Leiria U-1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MarathonBet(DK)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Leiria U-19 – Sporting Lisboa U-19Portugal. National Junior Championship A. 1st Division. South</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>H 2 (−0.25)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19/10 14:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sisal(IT)Football | Moins que 0.51re équipe | USD Castel</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sisal(IT)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USD Castellanzese 1921 – ASD Calcio BrusaportoITA Serie D</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 0.51re équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/10 13:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PointsBet(AU)Football | Plus que 7.5 - corners2e équipe | FC Copenha</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PointsBet(AU)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FC Copenhagen – Borussia DortmundEurope - UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - corners2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21/10 19:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PointsBet(AU)Football | Plus que 2.51re période2e équipe | Atlanta Ut</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PointsBet(AU)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atlanta Utd – DC UtdUnited States of America - MLS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re période2e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18/10 22:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FB SportsFootball | 1(0:1)1re période | Nanjing Ci</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FB SportsFootball</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Nanjing City – Jiangxi Dingnan United FCChina - Chinese League One</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1(0:1)1re période</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19/10 11:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8,40%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pixbet285Football | Plus que 1.51re équipe | HNK Cibali</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pixbet285Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HNK Cibalia – NK DugopoljeCroácia - 1.NL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 1.51re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19/10 13:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FB SportsFootball | 1(0:1)1re période | Orsomarso </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FB SportsFootball</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Orsomarso SC – Deportes QuindioColombia - Colombia Primera B</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1(0:1)1re période</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/10 22:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>14.70</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BaltBet(RU)Football | 1 | Фламенго Ж</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BaltBet(RU)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Фламенго Жапаратуба – Росарио Централ СержипеБразилия. Сержипано 2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>18/10 18:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>69,2%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MarathonBet(DK)Football | Pas de buts | Charlton A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MarathonBet(DK)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Charlton Athletic U-21 – Watford U-21England. Professional Development League 2 U-21</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>21/10 12:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>33.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bet9jaFootball | Pas de corners | Stormvogel</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bet9jaFootball</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Stormvogels Telstar – HeerenveenNetherlands - Eredivisie</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de corners</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19/10 10:15</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NairaBetFootball | Plus que 12.5 - corners | Coritiba F</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NairaBetFootball</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Coritiba FC PR – CA Paranaense PRBrazil - Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - corners</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19/10 21:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Fortuna(CZ)Tennis | Moins que 11.5 - aces | Alexandrov</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fortuna(CZ)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Alexandrova E. – Rybakina E.W-WTA Ningbo, singles</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - aces</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19/10 09:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>45,3%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Onabet(BR)Basketball | X1re période[race to 10 regular time] | Minas TC –</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Onabet(BR)Basketball</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Minas TC – SC Corinthians PaulistaBrazil - NBB</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>X1re période[race to 10 regular time]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>18/10 21:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TippmixPro(HU)Basketball | Plus que 21.51re période2e équipe | AEO Protea</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TippmixPro(HU)Basketball</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AEO Proteas Voulas (W) – Panathinaikos BC (W)Greece - A1 Women 2025/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 21.51re période2e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19/10 10:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FB SportsFootball | 2 - corners [race to 5 regular time] | FC Salzbur</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FB SportsFootball</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FC Salzburg – SCR AltachAustria - Austria Bundesliga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2 - corners [race to 5 regular time]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19/10 12:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BolsaDeAposta(BR)Football | Moins que 5.5- contre | Independie</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BolsaDeAposta(BR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia – BanfieldArgentina - Argentina Liga Profesional de Fútbol</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 5.5- contre</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>18/10 18:45</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>51.00(1,0%)1.02</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NetBet(BR)Football | Buts: Non1re équipe | Cruzeiro E</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NetBet(BR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cruzeiro EC – Fortaleza CEBrazil - Serie A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Buts: Non1re équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19/10 00:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Bet365(Full)Basketball | X1re période[race to 20 regular time] | Adelaide L</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bet365(Full)Basketball</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Adelaide Lightning (W) – Perth Lynx (W)Australia WNBL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>X1re période[race to 20 regular time]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19/10 07:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vivasorte(BR)Football | Pas de corners1re période | Genoa CFC </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vivasorte(BR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Genoa CFC – Parma CalcioItaly - Serie A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de corners1re période</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19/10 13:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>57.10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MarathonBet(IT)Football | 2(1:0)2e période | Ajax – Az </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MarathonBet(IT)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ajax – Az AlkmaarOlanda - Eredivisie</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2(1:0)2e période</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>18/10 19:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45948.72032509647</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="46">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="47">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="48">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="49">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="50">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="51">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="52">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="53">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="54">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="55">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="56">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="57">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="58">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="59">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="60">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="61">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="62">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="63">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="64">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="65">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="66">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="67">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="68">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
     <row r="69">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45948.72032509647</v>
+        <v>45948.7203250926</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3453,6 +3453,141 @@
         <v>45948.7203250926</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Pioneers V</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pioneers Vorarlberg – Olimpija LjubljanaAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19/10 14:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45948.84818607406</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Ocelari TrinecExtraliga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>21/10 16:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45948.84818607406</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – Mountfield HKExtraliga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>21/10 15:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45948.84818607406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-18.xlsx
+++ b/data/valuebets_database_2025-10-18.xlsx
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45948.84818607406</v>
+        <v>45948.84818607639</v>
       </c>
     </row>
     <row r="71">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45948.84818607406</v>
+        <v>45948.84818607639</v>
       </c>
     </row>
     <row r="72">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45948.84818607406</v>
+        <v>45948.84818607639</v>
       </c>
     </row>
   </sheetData>
